--- a/clean/economics/cice_listings_2026-10-15.xlsx
+++ b/clean/economics/cice_listings_2026-10-15.xlsx
@@ -422,7 +422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M40"/>
+  <dimension ref="A1:M35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -673,12 +673,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Business School</t>
+          <t>BAY AREA INTERNATIONAL BUSINESS SCHOOL</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=96DC1B7F3204BD16</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=4AC7F281ECBD2BA4</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -688,7 +688,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=96DC1B7F3204BD16</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=4AC7F281ECBD2BA4</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -705,17 +705,17 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Beijing Normal University</t>
+          <t>Capital University of Economics and Business</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>BAY AREA INTERNATIONAL BUSINESS SCHOOL</t>
+          <t>International School of Economics and Management</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=4AC7F281ECBD2BA4</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=230A8F8CAE8FB702</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -725,7 +725,7 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=4AC7F281ECBD2BA4</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=230A8F8CAE8FB702</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -742,17 +742,17 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Capital University of Economics and Business</t>
+          <t>Dongbei University of Finance &amp; Economics</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>International School of Economics and Management</t>
+          <t>Dongbei University Of Finance And Economics</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=230A8F8CAE8FB702</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=9058523321C2911A</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -762,7 +762,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=230A8F8CAE8FB702</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=9058523321C2911A</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -779,17 +779,17 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Dongbei University of Finance &amp; Economics</t>
+          <t>Donghua University</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Dongbei University Of Finance And Economics</t>
+          <t>Glorious Sun School of Business and Management</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=9058523321C2911A</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=1CE68DDB85B84365</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -799,7 +799,7 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=9058523321C2911A</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=1CE68DDB85B84365</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -816,17 +816,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Donghua University</t>
+          <t>Fudan University</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Glorious Sun School of Business and Management</t>
+          <t>School of Economics</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2026-11-01</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=1CE68DDB85B84365</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=E968D280DD59D564</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -836,7 +841,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=1CE68DDB85B84365</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=E968D280DD59D564</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -858,17 +863,17 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>School of Economics</t>
+          <t>School of Management</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-11-01</t>
+          <t>Rolling</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=E968D280DD59D564</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=E153FEE8CC8E11B5</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -878,7 +883,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=E968D280DD59D564</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=E153FEE8CC8E11B5</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -895,7 +900,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Fudan University</t>
+          <t>Harbin Institute of Technology</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -903,14 +908,9 @@
           <t>School of Management</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Rolling</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=E153FEE8CC8E11B5</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=3ED8A58471D2F80B</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -920,7 +920,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=E153FEE8CC8E11B5</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=3ED8A58471D2F80B</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -937,17 +937,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Harbin Institute of Technology</t>
+          <t>Huazhong University of Science and Technology</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>School of Management</t>
+          <t>School of Economics, Huazhong University of Science &amp; Technology</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=3ED8A58471D2F80B</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=A380FA8882023C78</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>CV; Job Market Paper; Letters of Reference</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -957,7 +962,7 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=3ED8A58471D2F80B</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=A380FA8882023C78</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -974,22 +979,17 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Huazhong University of Science and Technology</t>
+          <t>Hunan University</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>School of Economics, Huazhong University of Science &amp; Technology</t>
+          <t>School of Economics and Trade</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=A380FA8882023C78</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>CV; Job Market Paper; Letters of Reference</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=38CE3CA2770AB83B</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -999,7 +999,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=A380FA8882023C78</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=38CE3CA2770AB83B</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1016,17 +1016,17 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Hunan University</t>
+          <t>Jilin University</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>School of Economics and Trade</t>
+          <t>Business School</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=38CE3CA2770AB83B</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=A4E054BFC7078E2F</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1036,7 +1036,7 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=38CE3CA2770AB83B</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=A4E054BFC7078E2F</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1053,17 +1053,17 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Jilin University</t>
+          <t>Lanzhou University of Finance and Economics</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Business School</t>
+          <t>the Office of Personnel</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=A4E054BFC7078E2F</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=003923B6EFE42FFF</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1073,7 +1073,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=A4E054BFC7078E2F</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=003923B6EFE42FFF</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1090,17 +1090,17 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Lanzhou University of Finance and Economics</t>
+          <t>Nanjing Agricultural University</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>the Office of Personnel</t>
+          <t>College of Finance</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=003923B6EFE42FFF</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=41CE1E8D1AE20F34</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1110,7 +1110,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=003923B6EFE42FFF</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=41CE1E8D1AE20F34</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1127,17 +1127,17 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Nanjing Agricultural University</t>
+          <t>Nanjing University</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>College of Finance</t>
+          <t>Business School</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=41CE1E8D1AE20F34</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=5EE87D5DE6734D4D</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=41CE1E8D1AE20F34</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=5EE87D5DE6734D4D</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -1164,17 +1164,17 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Nanjing University</t>
+          <t>Nankai University</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Business School</t>
+          <t>School of Finance</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=5EE87D5DE6734D4D</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=96728BEC2B0A48B6</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1184,7 +1184,7 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=5EE87D5DE6734D4D</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=96728BEC2B0A48B6</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1201,17 +1201,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Nankai University</t>
+          <t>Peking University</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>School of Finance</t>
+          <t>Guanghua School of Management</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Rolling</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=96728BEC2B0A48B6</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=B2D1A3FBC0575542</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1221,7 +1226,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=96728BEC2B0A48B6</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=B2D1A3FBC0575542</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1243,17 +1248,17 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Guanghua School of Management</t>
+          <t>Peking University HSBC Business School</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rolling</t>
+          <t>2026-12-08</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=B2D1A3FBC0575542</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=6AA44C52147BF1AA</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1263,7 +1268,7 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=B2D1A3FBC0575542</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=6AA44C52147BF1AA</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -1280,22 +1285,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Peking University</t>
+          <t>Renmin University of China</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Peking University HSBC Business School</t>
+          <t>School of Finance, Renmin University of China</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-12-08</t>
+          <t>2026-12-01</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=6AA44C52147BF1AA</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=A2C98A6CF51DA6B8</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -1305,7 +1310,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=6AA44C52147BF1AA</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=A2C98A6CF51DA6B8</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -1322,17 +1327,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Remin University</t>
+          <t>Shanghai Jiao Tong University</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>School of Applied Economics</t>
+          <t>Antai College of Economics and Management</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-11-15</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=680004BD3C688FB5</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=A718B6651C5FE241</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -1342,7 +1352,7 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=680004BD3C688FB5</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=A718B6651C5FE241</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -1359,22 +1369,17 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Renmin University of China</t>
+          <t>Shanghai University of Finance Economics School</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>School of Finance, Renmin University of China</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>2026-12-01</t>
+          <t>School of Digital Economy</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=A2C98A6CF51DA6B8</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=7E509CEAE1E65959</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -1384,7 +1389,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=A2C98A6CF51DA6B8</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=7E509CEAE1E65959</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -1401,22 +1406,17 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Shanghai Jiao Tong University</t>
+          <t>Shanghai University of Finance and Economics</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Antai College of Economics and Management</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>2026-11-15</t>
+          <t>School of Economics</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=A718B6651C5FE241</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=3E6981392FF08E75</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -1426,7 +1426,7 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=A718B6651C5FE241</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=3E6981392FF08E75</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -1443,17 +1443,17 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Shanghai University of Finance Economics School</t>
+          <t>Southwestern University of Finance and Economics</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>School of Digital Economy</t>
+          <t>School of Economics</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=7E509CEAE1E65959</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=8F2A4E7B41A62BEC</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -1463,7 +1463,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=7E509CEAE1E65959</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=8F2A4E7B41A62BEC</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -1480,17 +1480,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Shanghai University of Finance and Economics</t>
+          <t>Tsinghua University</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>School of Economics</t>
+          <t>School of Economics and Management</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-11-30</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=3E6981392FF08E75</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=EB34146E1220A115</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -1500,7 +1505,7 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=3E6981392FF08E75</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=EB34146E1220A115</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -1517,17 +1522,17 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Shanghai University of Finance and Economics</t>
+          <t>Tsinghua University</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Dishui Lake Advanced Finance Institute</t>
+          <t>Center for International Finance and Economics Research</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=5D5B5B1874A95B18</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=6A1E66715A3A82D9</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -1537,7 +1542,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=5D5B5B1874A95B18</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=6A1E66715A3A82D9</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -1554,17 +1559,17 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Southwestern University of Finance and Economics</t>
+          <t>University of Electronic Science and Technology of China</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>School of Economics</t>
+          <t>School of Management and Economics</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=8F2A4E7B41A62BEC</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=390B333672086D05</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -1574,7 +1579,7 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=8F2A4E7B41A62BEC</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=390B333672086D05</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -1591,17 +1596,17 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Tongji University</t>
+          <t>University of Science and Technology of China</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>nothing</t>
+          <t>School of Management</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=41EFAE6DC817CCD8</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=6CAF00207D46BD36</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -1611,7 +1616,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=41EFAE6DC817CCD8</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=6CAF00207D46BD36</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -1628,17 +1633,17 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Tsinghua University</t>
+          <t>University of Science and Technology of China</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>School of Social Sciences</t>
+          <t>Institute of International Finance</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=48673CE5E9319FD6</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=612A2FEECB1FB3D7</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -1648,7 +1653,7 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=48673CE5E9319FD6</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=612A2FEECB1FB3D7</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -1665,22 +1670,17 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Tsinghua University</t>
+          <t>Xi%u2019an Jiaotong University</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>School of Economics and Management</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>2026-11-30</t>
+          <t>School of Economics and Finance</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=EB34146E1220A115</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=C3A72C51D391769E</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -1690,7 +1690,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=EB34146E1220A115</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=C3A72C51D391769E</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Tsinghua University</t>
+          <t>Xi%u2019an Jiaotong-Liverpool University</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Center for International Finance and Economics Research</t>
+          <t>International Business School Suzhou (IBSS), Department of Economics</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=6A1E66715A3A82D9</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=038CBF83FD61166B</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -1727,7 +1727,7 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=6A1E66715A3A82D9</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=038CBF83FD61166B</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -1744,17 +1744,17 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>University of Electronic Science and Technology of China</t>
+          <t>Zhejiang University</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>School of Management and Economics</t>
+          <t>International Business School</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=390B333672086D05</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=AB6EF80CCC4E40B3</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -1764,7 +1764,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=390B333672086D05</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=AB6EF80CCC4E40B3</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -1781,17 +1781,17 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>University of Science and Technology of China</t>
+          <t>Zhongnan Unviersity of Economics and Law</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>School of Management</t>
+          <t>School of Finance</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=6CAF00207D46BD36</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=2FC3B168FE2DBD23</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -1801,195 +1801,10 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=6CAF00207D46BD36</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=2FC3B168FE2DBD23</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
-        <is>
-          <t>Faculty</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>China</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>University of Science and Technology of China</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>Institute of International Finance</t>
-        </is>
-      </c>
-      <c r="H36" s="2" t="inlineStr">
-        <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=612A2FEECB1FB3D7</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>CICE</t>
-        </is>
-      </c>
-      <c r="K36" s="2" t="inlineStr">
-        <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=612A2FEECB1FB3D7</t>
-        </is>
-      </c>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>Faculty</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>China</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Xi%u2019an Jiaotong University</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>School of Economics and Finance</t>
-        </is>
-      </c>
-      <c r="H37" s="2" t="inlineStr">
-        <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=C3A72C51D391769E</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>CICE</t>
-        </is>
-      </c>
-      <c r="K37" s="2" t="inlineStr">
-        <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=C3A72C51D391769E</t>
-        </is>
-      </c>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>Faculty</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>China</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Xi%u2019an Jiaotong-Liverpool University</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>International Business School Suzhou (IBSS), Department of Economics</t>
-        </is>
-      </c>
-      <c r="H38" s="2" t="inlineStr">
-        <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=038CBF83FD61166B</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>CICE</t>
-        </is>
-      </c>
-      <c r="K38" s="2" t="inlineStr">
-        <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=038CBF83FD61166B</t>
-        </is>
-      </c>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>Faculty</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>China</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Zhejiang University</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>International Business School</t>
-        </is>
-      </c>
-      <c r="H39" s="2" t="inlineStr">
-        <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=AB6EF80CCC4E40B3</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>CICE</t>
-        </is>
-      </c>
-      <c r="K39" s="2" t="inlineStr">
-        <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=AB6EF80CCC4E40B3</t>
-        </is>
-      </c>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>Faculty</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>China</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Zhongnan Unviersity of Economics and Law</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>School of Finance</t>
-        </is>
-      </c>
-      <c r="H40" s="2" t="inlineStr">
-        <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=2FC3B168FE2DBD23</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>CICE</t>
-        </is>
-      </c>
-      <c r="K40" s="2" t="inlineStr">
-        <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=2FC3B168FE2DBD23</t>
-        </is>
-      </c>
-      <c r="M40" t="inlineStr">
         <is>
           <t>Faculty</t>
         </is>
@@ -2065,16 +1880,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K34" r:id="rId66"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H35" r:id="rId67"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K35" r:id="rId68"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H36" r:id="rId69"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K36" r:id="rId70"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H37" r:id="rId71"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K37" r:id="rId72"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H38" r:id="rId73"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K38" r:id="rId74"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H39" r:id="rId75"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K39" r:id="rId76"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H40" r:id="rId77"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K40" r:id="rId78"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/clean/economics/cice_listings_2026-10-15.xlsx
+++ b/clean/economics/cice_listings_2026-10-15.xlsx
@@ -422,7 +422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M35"/>
+  <dimension ref="A1:M33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -515,17 +515,22 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Anhui University of Finance and Economics</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>School of Economics</t>
+          <t>Beijing Jiaotong University School of Economics and Management</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Rolling</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=D43F9930BDD332A2</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=223BE806CD01DB59</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>CV; Job Market Paper; Letters of Reference</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -535,7 +540,7 @@
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=D43F9930BDD332A2</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=223BE806CD01DB59</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -552,17 +557,17 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Ant Group Research</t>
+          <t>Beijing Normal University</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Full-time Postdoctoral Researcher</t>
+          <t>BAY AREA INTERNATIONAL BUSINESS SCHOOL</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=BE0705D307C4EA24</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=4AC7F281ECBD2BA4</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -572,7 +577,7 @@
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=BE0705D307C4EA24</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=4AC7F281ECBD2BA4</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -589,17 +594,17 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Beijing Institute of Technology</t>
+          <t>Dongbei University of Finance &amp; Economics</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>School of Management and Economics</t>
+          <t>Dongbei University Of Finance And Economics</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=1D0A7E0E5861506A</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=9058523321C2911A</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -609,7 +614,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=1D0A7E0E5861506A</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=9058523321C2911A</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -626,22 +631,17 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Beijing Jiaotong University School of Economics and Management</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Rolling</t>
+          <t>Donghua University</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Glorious Sun School of Business and Management</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=223BE806CD01DB59</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>CV; Job Market Paper; Letters of Reference</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=1CE68DDB85B84365</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -651,7 +651,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=223BE806CD01DB59</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=1CE68DDB85B84365</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -668,17 +668,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Beijing Normal University</t>
+          <t>Fudan University</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>BAY AREA INTERNATIONAL BUSINESS SCHOOL</t>
+          <t>School of Economics</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>2026-11-01</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=4AC7F281ECBD2BA4</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=E968D280DD59D564</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -688,7 +693,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=4AC7F281ECBD2BA4</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=E968D280DD59D564</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -705,17 +710,17 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Capital University of Economics and Business</t>
+          <t>Harbin Institute of Technology</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>International School of Economics and Management</t>
+          <t>School of Management</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=230A8F8CAE8FB702</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=3ED8A58471D2F80B</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -725,7 +730,7 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=230A8F8CAE8FB702</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=3ED8A58471D2F80B</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -742,17 +747,17 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Dongbei University of Finance &amp; Economics</t>
+          <t>Lanzhou University of Finance and Economics</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Dongbei University Of Finance And Economics</t>
+          <t>the Office of Personnel</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=9058523321C2911A</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=003923B6EFE42FFF</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -762,7 +767,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=9058523321C2911A</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=003923B6EFE42FFF</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -779,17 +784,17 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Donghua University</t>
+          <t>Nanjing Agricultural University</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Glorious Sun School of Business and Management</t>
+          <t>College of Finance</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=1CE68DDB85B84365</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=41CE1E8D1AE20F34</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -799,7 +804,7 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=1CE68DDB85B84365</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=41CE1E8D1AE20F34</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -816,22 +821,17 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Fudan University</t>
+          <t>Nanjing University</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>School of Economics</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>2026-11-01</t>
+          <t>Business School</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=E968D280DD59D564</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=5EE87D5DE6734D4D</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -841,7 +841,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=E968D280DD59D564</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=5EE87D5DE6734D4D</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Fudan University</t>
+          <t>Peking University</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>School of Management</t>
+          <t>Guanghua School of Management</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -873,7 +873,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=E153FEE8CC8E11B5</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=B2D1A3FBC0575542</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -883,7 +883,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=E153FEE8CC8E11B5</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=B2D1A3FBC0575542</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -900,17 +900,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Harbin Institute of Technology</t>
+          <t>Peking University</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>School of Management</t>
+          <t>Peking University HSBC Business School</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2026-12-08</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=3ED8A58471D2F80B</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=6AA44C52147BF1AA</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -920,7 +925,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=3ED8A58471D2F80B</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=6AA44C52147BF1AA</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -937,22 +942,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Huazhong University of Science and Technology</t>
+          <t>Renmin University of China</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>School of Economics, Huazhong University of Science &amp; Technology</t>
+          <t>School of Finance, Renmin University of China</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2026-12-01</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=A380FA8882023C78</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>CV; Job Market Paper; Letters of Reference</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=A2C98A6CF51DA6B8</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -962,7 +967,7 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=A380FA8882023C78</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=A2C98A6CF51DA6B8</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -979,17 +984,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Hunan University</t>
+          <t>Shanghai Institute for Mathematics and Interdisciplinary Sciences</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>School of Economics and Trade</t>
+          <t>The Shanghai Institute for Mathematics and Interdisciplinary Sciences</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Rolling</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=38CE3CA2770AB83B</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=D6296C379B46AFF9</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -999,7 +1009,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=38CE3CA2770AB83B</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=D6296C379B46AFF9</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1016,17 +1026,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Jilin University</t>
+          <t>Shanghai Jiao Tong University</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Business School</t>
+          <t>Antai College of Economics and Management</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-11-15</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=A4E054BFC7078E2F</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=A718B6651C5FE241</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1036,7 +1051,7 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=A4E054BFC7078E2F</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=A718B6651C5FE241</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1053,17 +1068,17 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Lanzhou University of Finance and Economics</t>
+          <t>Shanghai University of Finance and Economics</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>the Office of Personnel</t>
+          <t>School of Economics</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=003923B6EFE42FFF</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=3E6981392FF08E75</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1073,7 +1088,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=003923B6EFE42FFF</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=3E6981392FF08E75</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1090,17 +1105,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Nanjing Agricultural University</t>
+          <t>Tsinghua University</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>College of Finance</t>
+          <t>School of Economics and Management</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-11-30</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=41CE1E8D1AE20F34</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=EB34146E1220A115</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1110,7 +1130,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=41CE1E8D1AE20F34</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=EB34146E1220A115</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1127,17 +1147,17 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Nanjing University</t>
+          <t>University of Science and Technology of China</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Business School</t>
+          <t>School of Management</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=5EE87D5DE6734D4D</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=6CAF00207D46BD36</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1147,7 +1167,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=5EE87D5DE6734D4D</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=6CAF00207D46BD36</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -1164,17 +1184,17 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Nankai University</t>
+          <t>Xi%u2019an Jiaotong University</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>School of Finance</t>
+          <t>School of Economics and Finance</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=96728BEC2B0A48B6</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=C3A72C51D391769E</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1184,7 +1204,7 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=96728BEC2B0A48B6</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=C3A72C51D391769E</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1201,22 +1221,17 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Peking University</t>
+          <t>Xi%u2019an Jiaotong-Liverpool University</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Guanghua School of Management</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Rolling</t>
+          <t>International Business School Suzhou (IBSS), Department of Economics</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=B2D1A3FBC0575542</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=038CBF83FD61166B</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1226,7 +1241,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=B2D1A3FBC0575542</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=038CBF83FD61166B</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1243,22 +1258,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Peking University</t>
+          <t>Zhejiang University</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Peking University HSBC Business School</t>
+          <t>School of Economics</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-12-08</t>
+          <t>Rolling</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=6AA44C52147BF1AA</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=7D928B7B1C35099A</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1268,7 +1283,7 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=6AA44C52147BF1AA</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=7D928B7B1C35099A</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -1285,22 +1300,17 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Renmin University of China</t>
+          <t>Zhongnan Unviersity of Economics and Law</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>School of Finance, Renmin University of China</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>2026-12-01</t>
+          <t>School of Finance</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=A2C98A6CF51DA6B8</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=2FC3B168FE2DBD23</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -1310,7 +1320,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=A2C98A6CF51DA6B8</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=2FC3B168FE2DBD23</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -1327,22 +1337,17 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Shanghai Jiao Tong University</t>
+          <t>Anhui University of Finance and Economics</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Antai College of Economics and Management</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>2026-11-15</t>
+          <t>School of Economics</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=A718B6651C5FE241</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=D43F9930BDD332A2</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -1352,12 +1357,12 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=A718B6651C5FE241</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=D43F9930BDD332A2</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>Faculty</t>
+          <t>Postdoc</t>
         </is>
       </c>
     </row>
@@ -1369,17 +1374,17 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Shanghai University of Finance Economics School</t>
+          <t>Ant Group Research</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>School of Digital Economy</t>
+          <t>Full-time Postdoctoral Researcher</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=7E509CEAE1E65959</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=BE0705D307C4EA24</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -1389,12 +1394,12 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=7E509CEAE1E65959</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=BE0705D307C4EA24</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>Faculty</t>
+          <t>Postdoc</t>
         </is>
       </c>
     </row>
@@ -1406,17 +1411,17 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Shanghai University of Finance and Economics</t>
+          <t>Beijing Institute of Technology</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>School of Economics</t>
+          <t>School of Management and Economics</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=3E6981392FF08E75</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=1D0A7E0E5861506A</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -1426,12 +1431,12 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=3E6981392FF08E75</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=1D0A7E0E5861506A</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>Faculty</t>
+          <t>Postdoc</t>
         </is>
       </c>
     </row>
@@ -1443,17 +1448,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Southwestern University of Finance and Economics</t>
+          <t>Fudan University</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>School of Economics</t>
+          <t>School of Management</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Rolling</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=8F2A4E7B41A62BEC</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=E153FEE8CC8E11B5</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -1463,12 +1473,12 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=8F2A4E7B41A62BEC</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=E153FEE8CC8E11B5</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>Faculty</t>
+          <t>Postdoc</t>
         </is>
       </c>
     </row>
@@ -1480,22 +1490,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Tsinghua University</t>
+          <t>Huazhong University of Science and Technology</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>School of Economics and Management</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>2026-11-30</t>
+          <t>School of Economics, Huazhong University of Science &amp; Technology</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=EB34146E1220A115</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=A380FA8882023C78</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>CV; Job Market Paper; Letters of Reference</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -1505,12 +1515,12 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=EB34146E1220A115</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=A380FA8882023C78</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>Faculty</t>
+          <t>Postdoc</t>
         </is>
       </c>
     </row>
@@ -1522,17 +1532,17 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Tsinghua University</t>
+          <t>Hunan University</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Center for International Finance and Economics Research</t>
+          <t>School of Economics and Trade</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=6A1E66715A3A82D9</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=38CE3CA2770AB83B</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -1542,12 +1552,12 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=6A1E66715A3A82D9</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=38CE3CA2770AB83B</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>Faculty</t>
+          <t>Postdoc</t>
         </is>
       </c>
     </row>
@@ -1559,17 +1569,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>University of Electronic Science and Technology of China</t>
+          <t>Sun Yat-sen University</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>School of Management and Economics</t>
+          <t>Lingnan College</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Rolling</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=390B333672086D05</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=73CF283104D9C7BB</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -1579,12 +1594,12 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=390B333672086D05</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=73CF283104D9C7BB</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>Faculty</t>
+          <t>Postdoc</t>
         </is>
       </c>
     </row>
@@ -1596,17 +1611,17 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>University of Science and Technology of China</t>
+          <t>Tsinghua University</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>School of Management</t>
+          <t>Center for International Finance and Economics Research</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=6CAF00207D46BD36</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=6A1E66715A3A82D9</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -1616,12 +1631,12 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=6CAF00207D46BD36</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=6A1E66715A3A82D9</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>Faculty</t>
+          <t>Postdoc</t>
         </is>
       </c>
     </row>
@@ -1633,17 +1648,17 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>University of Science and Technology of China</t>
+          <t>University of Electronic Science and Technology of China</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Institute of International Finance</t>
+          <t>School of Management and Economics</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=612A2FEECB1FB3D7</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=390B333672086D05</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -1653,12 +1668,12 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=612A2FEECB1FB3D7</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=390B333672086D05</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>Faculty</t>
+          <t>Postdoc</t>
         </is>
       </c>
     </row>
@@ -1670,17 +1685,17 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Xi%u2019an Jiaotong University</t>
+          <t>University of Science and Technology of China</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>School of Economics and Finance</t>
+          <t>Institute of International Finance</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=C3A72C51D391769E</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=612A2FEECB1FB3D7</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -1690,12 +1705,12 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=C3A72C51D391769E</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=612A2FEECB1FB3D7</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>Faculty</t>
+          <t>Postdoc</t>
         </is>
       </c>
     </row>
@@ -1707,17 +1722,17 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Xi%u2019an Jiaotong-Liverpool University</t>
+          <t>Zhejiang University</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>International Business School Suzhou (IBSS), Department of Economics</t>
+          <t>International Business School</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=038CBF83FD61166B</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=AB6EF80CCC4E40B3</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -1727,86 +1742,12 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=038CBF83FD61166B</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=AB6EF80CCC4E40B3</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>Faculty</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>China</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Zhejiang University</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>International Business School</t>
-        </is>
-      </c>
-      <c r="H34" s="2" t="inlineStr">
-        <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=AB6EF80CCC4E40B3</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>CICE</t>
-        </is>
-      </c>
-      <c r="K34" s="2" t="inlineStr">
-        <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=AB6EF80CCC4E40B3</t>
-        </is>
-      </c>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>Faculty</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>China</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Zhongnan Unviersity of Economics and Law</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>School of Finance</t>
-        </is>
-      </c>
-      <c r="H35" s="2" t="inlineStr">
-        <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=2FC3B168FE2DBD23</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>CICE</t>
-        </is>
-      </c>
-      <c r="K35" s="2" t="inlineStr">
-        <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=2FC3B168FE2DBD23</t>
-        </is>
-      </c>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>Faculty</t>
+          <t>Postdoc</t>
         </is>
       </c>
     </row>
@@ -1876,10 +1817,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K32" r:id="rId62"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H33" r:id="rId63"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K33" r:id="rId64"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H34" r:id="rId65"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K34" r:id="rId66"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H35" r:id="rId67"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K35" r:id="rId68"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
